--- a/portfolio_allocations/VWCE_allocation.xlsx
+++ b/portfolio_allocations/VWCE_allocation.xlsx
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.16039</v>
+        <v>0.15976</v>
       </c>
       <c r="F2" t="n">
-        <v>0.16134</v>
+        <v>0.16066</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.08053</v>
+        <v>0.08387</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08193</v>
+        <v>0.08717999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -541,14 +541,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.54144</v>
+        <v>1.59408</v>
       </c>
       <c r="F4" t="n">
-        <v>1.55623</v>
+        <v>1.61308</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.25712</v>
+        <v>0.2496</v>
       </c>
       <c r="F5" t="n">
-        <v>0.25567</v>
+        <v>0.25058</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -607,14 +607,14 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.43047</v>
+        <v>0.43007</v>
       </c>
       <c r="F6" t="n">
-        <v>0.42329</v>
+        <v>0.42475</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2.9095</v>
+        <v>3.0147</v>
       </c>
       <c r="F7" t="n">
-        <v>2.89226</v>
+        <v>3.00145</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -673,14 +673,14 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2.03553</v>
+        <v>1.96957</v>
       </c>
       <c r="F8" t="n">
-        <v>2.03205</v>
+        <v>1.98016</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.0694</v>
+        <v>0.06823</v>
       </c>
       <c r="F9" t="n">
-        <v>0.06884999999999999</v>
+        <v>0.0689</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -739,14 +739,14 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2.60705</v>
+        <v>2.72098</v>
       </c>
       <c r="F10" t="n">
-        <v>2.62341</v>
+        <v>2.73822</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -772,14 +772,14 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.0215</v>
+        <v>0.02378</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02298</v>
+        <v>0.02544</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -805,14 +805,14 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.0177</v>
+        <v>0.01914</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01375</v>
+        <v>0.01497</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -838,14 +838,14 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.82044</v>
+        <v>1.89345</v>
       </c>
       <c r="F13" t="n">
-        <v>1.82114</v>
+        <v>1.90172</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.35002</v>
+        <v>0.34817</v>
       </c>
       <c r="F14" t="n">
-        <v>0.34907</v>
+        <v>0.34877</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.00702</v>
+        <v>0.00648</v>
       </c>
       <c r="F15" t="n">
-        <v>0.00783</v>
+        <v>0.007849999999999999</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.84983</v>
+        <v>0.87449</v>
       </c>
       <c r="F16" t="n">
-        <v>0.85164</v>
+        <v>0.87493</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -970,14 +970,14 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.25597</v>
+        <v>0.24675</v>
       </c>
       <c r="F17" t="n">
-        <v>0.25572</v>
+        <v>0.24808</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1003,14 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2.01587</v>
+        <v>1.99452</v>
       </c>
       <c r="F18" t="n">
-        <v>2.02214</v>
+        <v>1.99502</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3.17585</v>
+        <v>3.25239</v>
       </c>
       <c r="F19" t="n">
-        <v>3.11501</v>
+        <v>3.19962</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1069,14 +1069,14 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.08064</v>
+        <v>0.091</v>
       </c>
       <c r="F20" t="n">
-        <v>0.08247</v>
+        <v>0.09093</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1102,14 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.43676</v>
+        <v>0.47797</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4389</v>
+        <v>0.47113</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1135,14 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.04634</v>
+        <v>0.04579</v>
       </c>
       <c r="F22" t="n">
-        <v>0.04501</v>
+        <v>0.04497</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1168,14 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.06388000000000001</v>
+        <v>0.07088</v>
       </c>
       <c r="F23" t="n">
-        <v>0.06289</v>
+        <v>0.07102</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1201,14 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.07663</v>
+        <v>0.08234</v>
       </c>
       <c r="F24" t="n">
-        <v>0.07701</v>
+        <v>0.08257</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.29951</v>
+        <v>0.29978</v>
       </c>
       <c r="F25" t="n">
-        <v>0.30244</v>
+        <v>0.30023</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1267,14 +1267,14 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1.59076</v>
+        <v>1.58938</v>
       </c>
       <c r="F26" t="n">
-        <v>1.59827</v>
+        <v>1.577</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1300,14 +1300,14 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.00843</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.00661</v>
+        <v>0.00683</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1333,14 +1333,14 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.80332</v>
+        <v>0.7971</v>
       </c>
       <c r="F28" t="n">
-        <v>0.79275</v>
+        <v>0.79714</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1366,14 +1366,14 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5.89522</v>
+        <v>5.99971</v>
       </c>
       <c r="F29" t="n">
-        <v>5.89726</v>
+        <v>5.98321</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1399,14 +1399,14 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2.9</v>
+        <v>2.49813</v>
       </c>
       <c r="F30" t="n">
-        <v>2.89436</v>
+        <v>2.49815</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1432,14 +1432,14 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.06042</v>
+        <v>0.06085</v>
       </c>
       <c r="F31" t="n">
-        <v>0.06544999999999999</v>
+        <v>0.06612</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1465,14 +1465,14 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.22126</v>
+        <v>0.21549</v>
       </c>
       <c r="F32" t="n">
-        <v>0.22524</v>
+        <v>0.22166</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1498,14 +1498,14 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.15053</v>
+        <v>0.15399</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1533</v>
+        <v>0.15727</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1531,14 +1531,14 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1.26122</v>
+        <v>1.14188</v>
       </c>
       <c r="F34" t="n">
-        <v>1.25358</v>
+        <v>1.13991</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1564,14 +1564,14 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.12832</v>
+        <v>0.14567</v>
       </c>
       <c r="F35" t="n">
-        <v>0.12607</v>
+        <v>0.14475</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1597,14 +1597,14 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.04927</v>
+        <v>0.05066</v>
       </c>
       <c r="F36" t="n">
-        <v>0.04838</v>
+        <v>0.05086</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1630,11 +1630,11 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.00045</v>
+        <v>2e-05</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1660,14 +1660,14 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.04284</v>
+        <v>0.03906</v>
       </c>
       <c r="F38" t="n">
-        <v>0.04221</v>
+        <v>0.04024</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1693,14 +1693,14 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.09721</v>
+        <v>0.111</v>
       </c>
       <c r="F39" t="n">
-        <v>0.10245</v>
+        <v>0.11476</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1726,14 +1726,14 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.04149</v>
+        <v>0.0437</v>
       </c>
       <c r="F40" t="n">
-        <v>0.04251</v>
+        <v>0.04456</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1759,14 +1759,14 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.06834</v>
+        <v>0.06511</v>
       </c>
       <c r="F41" t="n">
-        <v>0.06443</v>
+        <v>0.06048</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1792,14 +1792,14 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.01335</v>
+        <v>0.01287</v>
       </c>
       <c r="F42" t="n">
-        <v>0.01397</v>
+        <v>0.01387</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1855,14 +1855,14 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.31523</v>
+        <v>0.31946</v>
       </c>
       <c r="F44" t="n">
-        <v>0.32112</v>
+        <v>0.32467</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1888,14 +1888,14 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.69071</v>
+        <v>0.70719</v>
       </c>
       <c r="F45" t="n">
-        <v>0.69101</v>
+        <v>0.71155</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1921,14 +1921,14 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.3514</v>
+        <v>0.38336</v>
       </c>
       <c r="F46" t="n">
-        <v>0.34303</v>
+        <v>0.37681</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1954,14 +1954,14 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.15388</v>
+        <v>0.14899</v>
       </c>
       <c r="F47" t="n">
-        <v>0.15352</v>
+        <v>0.15272</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1987,14 +1987,14 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.09793</v>
+        <v>0.10003</v>
       </c>
       <c r="F48" t="n">
-        <v>0.10362</v>
+        <v>0.10074</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -2020,14 +2020,14 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3.37948</v>
+        <v>3.30919</v>
       </c>
       <c r="F49" t="n">
-        <v>3.38957</v>
+        <v>3.30465</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -2053,14 +2053,14 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>61.70329</v>
+        <v>61.68409</v>
       </c>
       <c r="F50" t="n">
-        <v>61.73505</v>
+        <v>61.71133</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -2086,14 +2086,14 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.36626</v>
+        <v>0.39658</v>
       </c>
       <c r="F51" t="n">
-        <v>0.37323</v>
+        <v>0.39848</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
